--- a/data/ams_weekly_data/Nexlev/ads_report_week34.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week34.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,42 +419,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -550,10 +538,10 @@
         <v>9498</v>
       </c>
       <c r="G4" t="n">
-        <v>951.4299999999999</v>
+        <v>1902.86</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1838,10 +1826,10 @@
         <v>8922</v>
       </c>
       <c r="G50" t="n">
-        <v>13724.58</v>
+        <v>16605.09</v>
       </c>
       <c r="H50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -2137,19 +2125,19 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>7785.16</v>
+        <v>7781.49</v>
       </c>
       <c r="E61" t="n">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="F61" t="n">
-        <v>92695</v>
+        <v>92694</v>
       </c>
       <c r="G61" t="n">
-        <v>24527.98</v>
+        <v>26222.05</v>
       </c>
       <c r="H61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62">
@@ -2314,10 +2302,10 @@
         <v>31785</v>
       </c>
       <c r="G67" t="n">
-        <v>8470.349999999999</v>
+        <v>10164.42</v>
       </c>
       <c r="H67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
@@ -2535,7 +2523,7 @@
         <v>345</v>
       </c>
       <c r="F75" t="n">
-        <v>78889</v>
+        <v>78890</v>
       </c>
       <c r="G75" t="n">
         <v>22474.58</v>
@@ -3294,10 +3282,10 @@
         <v>81736</v>
       </c>
       <c r="G102" t="n">
-        <v>8724.58</v>
+        <v>13215.26</v>
       </c>
       <c r="H102" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">
@@ -4803,7 +4791,7 @@
         <v>23</v>
       </c>
       <c r="F156" t="n">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -5195,7 +5183,7 @@
         <v>15</v>
       </c>
       <c r="F170" t="n">
-        <v>7369</v>
+        <v>7368</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -6091,7 +6079,7 @@
         <v>21</v>
       </c>
       <c r="F202" t="n">
-        <v>5824</v>
+        <v>5823</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -10655,7 +10643,7 @@
         <v>312</v>
       </c>
       <c r="F365" t="n">
-        <v>20726</v>
+        <v>20725</v>
       </c>
       <c r="G365" t="n">
         <v>8894.07</v>
@@ -10711,7 +10699,7 @@
         <v>1298</v>
       </c>
       <c r="F367" t="n">
-        <v>76873</v>
+        <v>76869</v>
       </c>
       <c r="G367" t="n">
         <v>32778.83</v>
@@ -10875,42 +10863,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -12135,47 +12123,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
@@ -12236,10 +12224,10 @@
         <v>5314.87</v>
       </c>
       <c r="G3" t="n">
-        <v>23887.31</v>
+        <v>24437.31</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -12623,19 +12611,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>23384</v>
+        <v>23638</v>
       </c>
       <c r="E15" t="n">
-        <v>1578</v>
+        <v>1596</v>
       </c>
       <c r="F15" t="n">
-        <v>11827.99428109269</v>
+        <v>11956.22211786854</v>
       </c>
       <c r="G15" t="n">
-        <v>167931.4537948256</v>
+        <v>174274.4274808932</v>
       </c>
       <c r="H15" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -12656,16 +12644,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5728</v>
+        <v>5659</v>
       </c>
       <c r="E16" t="n">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="F16" t="n">
-        <v>2897.263648545464</v>
+        <v>2862.116393487238</v>
       </c>
       <c r="G16" t="n">
-        <v>41134.7591962306</v>
+        <v>41718.33635586456</v>
       </c>
       <c r="H16" t="n">
         <v>12</v>
@@ -12689,16 +12677,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13538</v>
+        <v>13373</v>
       </c>
       <c r="E17" t="n">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="F17" t="n">
-        <v>6847.401109001476</v>
+        <v>6764.333986896493</v>
       </c>
       <c r="G17" t="n">
-        <v>97218.00633511042</v>
+        <v>98597.23424627124</v>
       </c>
       <c r="H17" t="n">
         <v>29</v>
@@ -12722,16 +12710,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1632</v>
+        <v>1612</v>
       </c>
       <c r="E18" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F18" t="n">
-        <v>825.4309613603682</v>
+        <v>815.4175017477251</v>
       </c>
       <c r="G18" t="n">
-        <v>11719.3006738334</v>
+        <v>11885.56191697102</v>
       </c>
       <c r="H18" t="n">
         <v>4</v>
@@ -12764,10 +12752,10 @@
         <v>3447.162943804401</v>
       </c>
       <c r="G19" t="n">
-        <v>36844.99620085592</v>
+        <v>39934.47632370573</v>
       </c>
       <c r="H19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -12797,7 +12785,7 @@
         <v>333.2370561955987</v>
       </c>
       <c r="G20" t="n">
-        <v>3561.803799144089</v>
+        <v>3860.463676294273</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
